--- a/artfynd/S 4218-2023 artfynd.xlsx
+++ b/artfynd/S 4218-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2301,69 +2301,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128648547</v>
+        <v>137532906</v>
       </c>
       <c r="B14" t="n">
-        <v>57966</v>
+        <v>99777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vaxsjön_2, Frostavallen, Sk</t>
+          <t>300 m SO vägkorset i Långstorp, Sk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407995</v>
+        <v>407798</v>
       </c>
       <c r="R14" t="n">
-        <v>6204130</v>
+        <v>6204630</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2390,22 +2366,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2416,31 +2382,36 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>bäckdråg i hagmark</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Simon Divall</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Simon Divall</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128648547</t>
+          <t>https://artportalen.se/Sighting/137532906</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105194737</v>
+        <v>137532345</v>
       </c>
       <c r="B15" t="n">
-        <v>57947</v>
+        <v>105149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2448,44 +2419,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102977</v>
+        <v>220461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vaxsjön, Höör, Sk, Sk</t>
+          <t>200 m NNO Vaxsjöns nordspets, Sk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407955</v>
+        <v>408100</v>
       </c>
       <c r="R15" t="n">
-        <v>6204129</v>
+        <v>6204464</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2512,12 +2473,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-12-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-12-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2528,31 +2489,36 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>källpåverkad medelrik lövskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Arvidsson</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Arvidsson</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105194737</t>
+          <t>https://artportalen.se/Sighting/137532345</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128648540</v>
+        <v>137531793</v>
       </c>
       <c r="B16" t="n">
-        <v>57947</v>
+        <v>111464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,54 +2526,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>221037</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vildkaprifol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lonicera periclymenum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Vaxsjön_2, Frostavallen, Sk</t>
+          <t>200 m NNO Vaxsjöns nordspets, Sk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407995</v>
+        <v>408100</v>
       </c>
       <c r="R16" t="n">
-        <v>6204130</v>
+        <v>6204464</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2634,22 +2580,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:05</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2660,69 +2596,74 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>källpåverkad medelrik lövskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Simon Divall</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Simon Divall</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128648540</t>
+          <t>https://artportalen.se/Sighting/137531793</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121183035</v>
+        <v>137532307</v>
       </c>
       <c r="B17" t="n">
-        <v>92342</v>
+        <v>106468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2023</v>
+        <v>221154</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lundagård, Lundagård, Sk</t>
+          <t>100 m V Vaxsjöns nordspets, Sk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408937</v>
+        <v>407971</v>
       </c>
       <c r="R17" t="n">
-        <v>6203851</v>
+        <v>6204333</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2746,22 +2687,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2772,78 +2703,74 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>lärkplantage</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jacob Björnberg</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jacob Björnberg</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121183035</t>
+          <t>https://artportalen.se/Sighting/137532307</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>100421535</v>
+        <v>137532630</v>
       </c>
       <c r="B18" t="n">
-        <v>103266</v>
+        <v>106679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>223143</v>
+        <v>221423</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Engelskt björnbär</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rubus echinatus</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lindley</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vid Skåneleden, Sk</t>
+          <t>200 m NNO Vaxsjöns nordspets, Sk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408868</v>
+        <v>408100</v>
       </c>
       <c r="R18" t="n">
-        <v>6203839</v>
+        <v>6204464</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2867,12 +2794,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-07-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2886,71 +2813,71 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>lövskog</t>
+          <t>källpåverkad medelrik lövskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ulf Ryde</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ulf Ryde</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100421535</t>
+          <t>https://artportalen.se/Sighting/137532630</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121199033</v>
+        <v>137531628</v>
       </c>
       <c r="B19" t="n">
-        <v>104232</v>
+        <v>107969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1896</v>
+        <v>221705</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödlånke</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lythrum portula</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) D. A. Webb</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Maglebjär, 800 m söder, Sk</t>
+          <t>100 m V Vaxsjöns nordspets, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409382</v>
+        <v>407971</v>
       </c>
       <c r="R19" t="n">
-        <v>6203278</v>
+        <v>6204333</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2974,17 +2901,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1947-08-22</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1947-08-22</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Inventerad av Gunnar Olsson</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2998,37 +2920,33 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Stig</t>
+          <t>lärkplantage</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Skånes Flora, Höör socken, 1946-1947</t>
-        </is>
-      </c>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121199033</t>
+          <t>https://artportalen.se/Sighting/137531628</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129363565</v>
+        <v>137532616</v>
       </c>
       <c r="B20" t="n">
-        <v>104282</v>
+        <v>104623</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3056,17 +2974,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>500 m SSV Maglebjär, Sk</t>
+          <t>200 m NNO Vaxsjöns nordspets, Sk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409211</v>
+        <v>408100</v>
       </c>
       <c r="R20" t="n">
-        <v>6203458</v>
+        <v>6204464</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3090,12 +3008,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3109,7 +3027,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>fuktigt skogsmaskinspår</t>
+          <t>källpåverkad medelrik lövskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3125,6 +3043,1475 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532616</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137532287</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100205</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>350 m OSO vägkorset i Långstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>407889</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6204571</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>längs skogsdike</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532287</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137532710</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101055</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222586</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lundslok</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Melica uniflora</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Retz.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>200 m NNO Vaxsjöns nordspets, Sk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>408100</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6204464</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>källpåverkad medelrik lövskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532710</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137531193</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99748</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222857</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ekorrbär</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Maianthemum bifolium</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) F. W. Schmidt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>vid (O) Vaxsjöns nordspets, Sk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>408181</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6204315</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>björksumpskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137531193</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137530839</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98489</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>350 m OSO vägkorset i Långstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>407889</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6204571</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>längs skogsdike</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137530839</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137532054</v>
+      </c>
+      <c r="B25" t="n">
+        <v>102191</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223366</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svarta vinbär</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ribes nigrum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>350 m OSO vägkorset i Långstorp, Sk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>407889</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6204571</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>längs skogsdike</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532054</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137531870</v>
+      </c>
+      <c r="B26" t="n">
+        <v>107669</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>224264</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vanlig gulplister</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lamiastrum galeobdolon subsp. galeobdolon</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>200 m NNO Vaxsjöns nordspets, Sk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>408100</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6204464</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>källpåverkad medelrik lövskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137531870</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128648547</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Vaxsjön_2, Frostavallen, Sk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>407995</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6204130</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Simon Divall</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Simon Divall</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128648547</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>105194737</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Vaxsjön, Höör, Sk, Sk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>407955</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6204129</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-12-16</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-12-16</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lisa Arvidsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lisa Arvidsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105194737</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128648540</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Vaxsjön_2, Frostavallen, Sk</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>407995</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6204130</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Simon Divall</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Simon Divall</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128648540</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121183035</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92342</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sydlig sotticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ischnoderma resinosum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Schrad.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lundagård, Lundagård, Sk</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>408937</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6203851</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-11-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jacob Björnberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121183035</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>100421535</v>
+      </c>
+      <c r="B31" t="n">
+        <v>103266</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>223143</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Engelskt björnbär</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rubus echinatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Lindley</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Vid Skåneleden, Sk</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>408868</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6203839</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2021-07-10</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ulf Ryde</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ulf Ryde</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100421535</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121199033</v>
+      </c>
+      <c r="B32" t="n">
+        <v>104232</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1896</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Rödlånke</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lythrum portula</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) D. A. Webb</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Maglebjär, 800 m söder, Sk</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>409382</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6203278</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>1947-08-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>1947-08-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Inventerad av Gunnar Olsson</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Stig</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Via Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Skånes Flora, Höör socken, 1946-1947</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121199033</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129363565</v>
+      </c>
+      <c r="B33" t="n">
+        <v>104282</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222075</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk dunört</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Epilobium obscurum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>500 m SSV Maglebjär, Sk</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>409211</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6203458</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>fuktigt skogsmaskinspår</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129363565</t>
         </is>
@@ -3151,6 +4538,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
